--- a/РАБОЧИЙ СТОЛ/расчет ПОКОМ ЗПФ/дв 16,07,26 днрсч пок зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет ПОКОМ ЗПФ/дв 16,07,26 днрсч пок зпф.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91AE6D7-9EDB-4682-AC5C-44E9C4FB96A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F756F42C-D868-48D4-8B93-97D19ADAFF12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="173">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -547,6 +547,9 @@
   </si>
   <si>
     <t>увеличил до 300шт - задача для ТК (10,07,26)</t>
+  </si>
+  <si>
+    <t>20,07,</t>
   </si>
 </sst>
 </file>
@@ -1314,7 +1317,9 @@
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
       <c r="AE4" s="7"/>
-      <c r="AF4" s="9"/>
+      <c r="AF4" s="9" t="s">
+        <v>172</v>
+      </c>
       <c r="AG4" s="5"/>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
